--- a/data/trans_dic/P3A$personadelacasa-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P3A$personadelacasa-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos otra persona se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona del hogar se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,56; 20,45</t>
+          <t>13,31; 20,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,02; 16,27</t>
+          <t>12,26; 16,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,36; 16,82</t>
+          <t>13,51; 17,22</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,02; 33,33</t>
+          <t>19,37; 33,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,09; 29,67</t>
+          <t>19,68; 29,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,85; 30,75</t>
+          <t>22,35; 30,97</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,89; 29,61</t>
+          <t>21,73; 29,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,47; 28,76</t>
+          <t>22,1; 28,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,12; 27,96</t>
+          <t>23,11; 27,99</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,88; 29,2</t>
+          <t>20,31; 29,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,07; 25,45</t>
+          <t>19,3; 25,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,56; 26,69</t>
+          <t>21,7; 26,6</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos otra persona se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona del hogar se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>69813; 105301</t>
+          <t>68558; 104874</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>90836; 122950</t>
+          <t>92661; 122795</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>169779; 213672</t>
+          <t>171619; 218710</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>435504; 762945</t>
+          <t>443390; 760875</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>404574; 663688</t>
+          <t>440052; 668458</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>989084; 1391707</t>
+          <t>1011334; 1401766</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>141528; 191468</t>
+          <t>140532; 192167</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>148377; 189939</t>
+          <t>145938; 190090</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>302152; 365482</t>
+          <t>302053; 365875</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>720533; 1007774</t>
+          <t>700755; 1005290</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>696429; 929429</t>
+          <t>704897; 928762</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1531790; 1895755</t>
+          <t>1541657; 1889266</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$personadelacasa-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P3A$personadelacasa-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,31; 20,37</t>
+          <t>13,45; 19,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,26; 16,25</t>
+          <t>12,07; 16,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,51; 17,22</t>
+          <t>13,57; 16,84</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,37; 33,24</t>
+          <t>28,55; 33,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,68; 29,89</t>
+          <t>27,97; 31,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,35; 30,97</t>
+          <t>29,01; 32,14</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,73; 29,72</t>
+          <t>21,95; 29,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,1; 28,78</t>
+          <t>21,77; 28,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,11; 27,99</t>
+          <t>22,87; 27,97</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,31; 29,13</t>
+          <t>25,74; 29,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,3; 25,43</t>
+          <t>23,97; 26,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,7; 26,6</t>
+          <t>25,33; 27,58</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85784</t>
+          <t>94132</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>105745</t>
+          <t>116165</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>191529</t>
+          <t>210298</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>68558; 104874</t>
+          <t>77829; 113512</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>92661; 122795</t>
+          <t>99250; 132507</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>171619; 218710</t>
+          <t>190088; 235892</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>658291</t>
+          <t>694053</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>578627</t>
+          <t>648717</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1236918</t>
+          <t>1342770</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>443390; 760875</t>
+          <t>636609; 749343</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>440052; 668458</t>
+          <t>607010; 694317</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1011334; 1401766</t>
+          <t>1276328; 1413962</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>164805</t>
+          <t>183423</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>168424</t>
+          <t>182299</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>333230</t>
+          <t>365721</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>140532; 192167</t>
+          <t>156204; 212270</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>145938; 190090</t>
+          <t>160001; 206414</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>302053; 365875</t>
+          <t>330774; 404618</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>908880</t>
+          <t>971608</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>852796</t>
+          <t>947181</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1761676</t>
+          <t>1918789</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>700755; 1005290</t>
+          <t>905855; 1033129</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>704897; 928762</t>
+          <t>893196; 1000612</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1541657; 1889266</t>
+          <t>1835780; 1998505</t>
         </is>
       </c>
     </row>
